--- a/diseases/d106/2005-2009.xlsx
+++ b/diseases/d106/2005-2009.xlsx
@@ -913,9 +913,6 @@
       <c r="O3" t="n">
         <v>63</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
         <v>1.200896211687122</v>
       </c>
@@ -1309,9 +1306,6 @@
       <c r="O5" t="n">
         <v>113</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
       <c r="R5" t="n">
         <v>2.444234677676826</v>
       </c>
@@ -1853,9 +1847,6 @@
       <c r="O8" t="n">
         <v>52</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0.9912159207576244</v>
       </c>
@@ -2249,9 +2240,6 @@
       <c r="O10" t="n">
         <v>110</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
         <v>2.379343491543813</v>
       </c>
@@ -2793,9 +2781,6 @@
       <c r="O13" t="n">
         <v>71</v>
       </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
       <c r="R13" t="n">
         <v>1.353390968726756</v>
       </c>
@@ -3189,9 +3174,6 @@
       <c r="O15" t="n">
         <v>128</v>
       </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
       <c r="R15" t="n">
         <v>2.768690608341892</v>
       </c>
@@ -3733,9 +3715,6 @@
       <c r="O18" t="n">
         <v>71</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="R18" t="n">
         <v>1.353390968726756</v>
       </c>
@@ -4129,9 +4108,6 @@
       <c r="O20" t="n">
         <v>89</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" t="n">
         <v>1.925105188612722</v>
       </c>
@@ -4673,9 +4649,6 @@
       <c r="O23" t="n">
         <v>95</v>
       </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
       <c r="R23" t="n">
         <v>1.81087523984566</v>
       </c>
@@ -5069,9 +5042,6 @@
       <c r="O25" t="n">
         <v>101</v>
       </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
       <c r="R25" t="n">
         <v>2.184669933144774</v>
       </c>
@@ -5613,9 +5583,6 @@
       <c r="O28" t="n">
         <v>60</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="R28" t="n">
         <v>1.143710677797259</v>
       </c>
@@ -6009,9 +5976,6 @@
       <c r="O30" t="n">
         <v>84</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
         <v>1.816953211724367</v>
       </c>
@@ -6553,9 +6517,6 @@
       <c r="O33" t="n">
         <v>27</v>
       </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
       <c r="R33" t="n">
         <v>0.5146698050087665</v>
       </c>
@@ -6949,9 +6910,6 @@
       <c r="O35" t="n">
         <v>35</v>
       </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
       <c r="R35" t="n">
         <v>0.757063838218486</v>
       </c>
@@ -7493,9 +7451,6 @@
       <c r="O38" t="n">
         <v>32</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="R38" t="n">
         <v>0.6099790281585381</v>
       </c>
@@ -7889,9 +7844,6 @@
       <c r="O40" t="n">
         <v>37</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="R40" t="n">
         <v>0.8003246289738281</v>
       </c>
@@ -8433,9 +8385,6 @@
       <c r="O43" t="n">
         <v>63</v>
       </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
       <c r="R43" t="n">
         <v>1.200896211687122</v>
       </c>
@@ -8829,9 +8778,6 @@
       <c r="O45" t="n">
         <v>87</v>
       </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
       <c r="R45" t="n">
         <v>1.88184439785738</v>
       </c>
@@ -9373,9 +9319,6 @@
       <c r="O48" t="n">
         <v>67</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="R48" t="n">
         <v>1.277143590206939</v>
       </c>
@@ -9769,9 +9712,6 @@
       <c r="O50" t="n">
         <v>92</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>1.989996374745735</v>
       </c>
@@ -10313,9 +10253,6 @@
       <c r="O53" t="n">
         <v>63</v>
       </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
       <c r="R53" t="n">
         <v>1.200896211687122</v>
       </c>
@@ -10709,9 +10646,6 @@
       <c r="O55" t="n">
         <v>81</v>
       </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
       <c r="R55" t="n">
         <v>1.752062025591353</v>
       </c>
@@ -11253,9 +11187,6 @@
       <c r="O58" t="n">
         <v>73</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="R58" t="n">
         <v>1.391514657986665</v>
       </c>
@@ -11649,9 +11580,6 @@
       <c r="O60" t="n">
         <v>125</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="R60" t="n">
         <v>2.703799422208879</v>
       </c>
@@ -12193,9 +12121,6 @@
       <c r="O63" t="n">
         <v>65</v>
       </c>
-      <c r="Q63" t="n">
-        <v>0</v>
-      </c>
       <c r="R63" t="n">
         <v>1.23427568382908</v>
       </c>
@@ -12589,9 +12514,6 @@
       <c r="O65" t="n">
         <v>108</v>
       </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
       <c r="R65" t="n">
         <v>2.317350907435993</v>
       </c>
@@ -13133,9 +13055,6 @@
       <c r="O68" t="n">
         <v>58</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="R68" t="n">
         <v>1.101353687109025</v>
       </c>
@@ -13529,9 +13448,6 @@
       <c r="O70" t="n">
         <v>102</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="R70" t="n">
         <v>2.188609190356215</v>
       </c>
@@ -14073,9 +13989,6 @@
       <c r="O73" t="n">
         <v>56</v>
       </c>
-      <c r="Q73" t="n">
-        <v>0</v>
-      </c>
       <c r="R73" t="n">
         <v>1.063375973760438</v>
       </c>
@@ -14469,9 +14382,6 @@
       <c r="O75" t="n">
         <v>71</v>
       </c>
-      <c r="Q75" t="n">
-        <v>0</v>
-      </c>
       <c r="R75" t="n">
         <v>1.523443652110699</v>
       </c>
@@ -15013,9 +14923,6 @@
       <c r="O78" t="n">
         <v>66</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="R78" t="n">
         <v>1.253264540503374</v>
       </c>
@@ -15409,9 +15316,6 @@
       <c r="O80" t="n">
         <v>98</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="R80" t="n">
         <v>2.102781378969697</v>
       </c>
@@ -15953,9 +15857,6 @@
       <c r="O83" t="n">
         <v>72</v>
       </c>
-      <c r="Q83" t="n">
-        <v>0</v>
-      </c>
       <c r="R83" t="n">
         <v>1.367197680549135</v>
       </c>
@@ -16349,9 +16250,6 @@
       <c r="O85" t="n">
         <v>113</v>
       </c>
-      <c r="Q85" t="n">
-        <v>0</v>
-      </c>
       <c r="R85" t="n">
         <v>2.424635671669141</v>
       </c>
@@ -16893,9 +16791,6 @@
       <c r="O88" t="n">
         <v>60</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="R88" t="n">
         <v>1.139331400457612</v>
       </c>
@@ -17289,9 +17184,6 @@
       <c r="O90" t="n">
         <v>89</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="R90" t="n">
         <v>1.909668803350031</v>
       </c>
@@ -17833,9 +17725,6 @@
       <c r="O93" t="n">
         <v>44</v>
       </c>
-      <c r="Q93" t="n">
-        <v>0</v>
-      </c>
       <c r="R93" t="n">
         <v>0.8355096936689158</v>
       </c>
@@ -18229,9 +18118,6 @@
       <c r="O95" t="n">
         <v>48</v>
       </c>
-      <c r="Q95" t="n">
-        <v>0</v>
-      </c>
       <c r="R95" t="n">
         <v>1.029933736638219</v>
       </c>
@@ -18773,9 +18659,6 @@
       <c r="O98" t="n">
         <v>38</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="R98" t="n">
         <v>0.7215765536231545</v>
       </c>
@@ -19169,9 +19052,6 @@
       <c r="O100" t="n">
         <v>26</v>
       </c>
-      <c r="Q100" t="n">
-        <v>0</v>
-      </c>
       <c r="R100" t="n">
         <v>0.5578807740123687</v>
       </c>
@@ -19713,9 +19593,6 @@
       <c r="O103" t="n">
         <v>62</v>
       </c>
-      <c r="Q103" t="n">
-        <v>0</v>
-      </c>
       <c r="R103" t="n">
         <v>1.1773091138062</v>
       </c>
@@ -20109,9 +19986,6 @@
       <c r="O105" t="n">
         <v>79</v>
       </c>
-      <c r="Q105" t="n">
-        <v>0</v>
-      </c>
       <c r="R105" t="n">
         <v>1.695099274883735</v>
       </c>
@@ -20653,9 +20527,6 @@
       <c r="O108" t="n">
         <v>82</v>
       </c>
-      <c r="Q108" t="n">
-        <v>0</v>
-      </c>
       <c r="R108" t="n">
         <v>1.55708624729207</v>
       </c>
@@ -21049,9 +20920,6 @@
       <c r="O110" t="n">
         <v>77</v>
       </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
       <c r="R110" t="n">
         <v>1.652185369190476</v>
       </c>
@@ -21593,9 +21461,6 @@
       <c r="O113" t="n">
         <v>71</v>
       </c>
-      <c r="Q113" t="n">
-        <v>0</v>
-      </c>
       <c r="R113" t="n">
         <v>1.348208823874842</v>
       </c>
@@ -21989,9 +21854,6 @@
       <c r="O115" t="n">
         <v>100</v>
       </c>
-      <c r="Q115" t="n">
-        <v>0</v>
-      </c>
       <c r="R115" t="n">
         <v>2.145695284662956</v>
       </c>
@@ -22533,9 +22395,6 @@
       <c r="O118" t="n">
         <v>72</v>
       </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
       <c r="R118" t="n">
         <v>1.367197680549135</v>
       </c>
@@ -22929,9 +22788,6 @@
       <c r="O120" t="n">
         <v>101</v>
       </c>
-      <c r="Q120" t="n">
-        <v>0</v>
-      </c>
       <c r="R120" t="n">
         <v>2.167152237509586</v>
       </c>
@@ -23473,9 +23329,6 @@
       <c r="O123" t="n">
         <v>56</v>
       </c>
-      <c r="Q123" t="n">
-        <v>0</v>
-      </c>
       <c r="R123" t="n">
         <v>1.058859343771922</v>
       </c>
@@ -23869,9 +23722,6 @@
       <c r="O125" t="n">
         <v>102</v>
       </c>
-      <c r="Q125" t="n">
-        <v>0</v>
-      </c>
       <c r="R125" t="n">
         <v>2.166060382118534</v>
       </c>
@@ -24413,9 +24263,6 @@
       <c r="O128" t="n">
         <v>77</v>
       </c>
-      <c r="Q128" t="n">
-        <v>0</v>
-      </c>
       <c r="R128" t="n">
         <v>1.455931597686392</v>
       </c>
@@ -24809,9 +24656,6 @@
       <c r="O130" t="n">
         <v>120</v>
       </c>
-      <c r="Q130" t="n">
-        <v>0</v>
-      </c>
       <c r="R130" t="n">
         <v>2.548306331904158</v>
       </c>
@@ -25353,9 +25197,6 @@
       <c r="O133" t="n">
         <v>82</v>
       </c>
-      <c r="Q133" t="n">
-        <v>0</v>
-      </c>
       <c r="R133" t="n">
         <v>1.550472610523171</v>
       </c>
@@ -25749,9 +25590,6 @@
       <c r="O135" t="n">
         <v>101</v>
       </c>
-      <c r="Q135" t="n">
-        <v>0</v>
-      </c>
       <c r="R135" t="n">
         <v>2.144824496019333</v>
       </c>
@@ -26293,9 +26131,6 @@
       <c r="O138" t="n">
         <v>70</v>
       </c>
-      <c r="Q138" t="n">
-        <v>0</v>
-      </c>
       <c r="R138" t="n">
         <v>1.323574179714902</v>
       </c>
@@ -26689,9 +26524,6 @@
       <c r="O140" t="n">
         <v>89</v>
       </c>
-      <c r="Q140" t="n">
-        <v>0</v>
-      </c>
       <c r="R140" t="n">
         <v>1.889993862828917</v>
       </c>
@@ -27233,9 +27065,6 @@
       <c r="O143" t="n">
         <v>98</v>
       </c>
-      <c r="Q143" t="n">
-        <v>0</v>
-      </c>
       <c r="R143" t="n">
         <v>1.853003851600863</v>
       </c>
@@ -27629,9 +27458,6 @@
       <c r="O145" t="n">
         <v>97</v>
       </c>
-      <c r="Q145" t="n">
-        <v>0</v>
-      </c>
       <c r="R145" t="n">
         <v>2.059880951622528</v>
       </c>
@@ -28173,9 +27999,6 @@
       <c r="O148" t="n">
         <v>58</v>
       </c>
-      <c r="Q148" t="n">
-        <v>0</v>
-      </c>
       <c r="R148" t="n">
         <v>1.096675748906633</v>
       </c>
@@ -28569,9 +28392,6 @@
       <c r="O150" t="n">
         <v>53</v>
       </c>
-      <c r="Q150" t="n">
-        <v>0</v>
-      </c>
       <c r="R150" t="n">
         <v>1.12550196325767</v>
       </c>
@@ -29113,9 +28933,6 @@
       <c r="O153" t="n">
         <v>45</v>
       </c>
-      <c r="Q153" t="n">
-        <v>0</v>
-      </c>
       <c r="R153" t="n">
         <v>0.8508691155310085</v>
       </c>
@@ -29509,9 +29326,6 @@
       <c r="O155" t="n">
         <v>36</v>
       </c>
-      <c r="Q155" t="n">
-        <v>0</v>
-      </c>
       <c r="R155" t="n">
         <v>0.7644918995712474</v>
       </c>
@@ -30053,9 +29867,6 @@
       <c r="O158" t="n">
         <v>39</v>
       </c>
-      <c r="Q158" t="n">
-        <v>0</v>
-      </c>
       <c r="R158" t="n">
         <v>0.7374199001268741</v>
       </c>
@@ -30449,9 +30260,6 @@
       <c r="O160" t="n">
         <v>37</v>
       </c>
-      <c r="Q160" t="n">
-        <v>0</v>
-      </c>
       <c r="R160" t="n">
         <v>0.7857277856704489</v>
       </c>
@@ -31141,9 +30949,6 @@
       <c r="O164" t="n">
         <v>74</v>
       </c>
-      <c r="Q164" t="n">
-        <v>0</v>
-      </c>
       <c r="R164" t="n">
         <v>1.399206989984325</v>
       </c>
@@ -31537,9 +31342,6 @@
       <c r="O166" t="n">
         <v>75</v>
       </c>
-      <c r="Q166" t="n">
-        <v>0</v>
-      </c>
       <c r="R166" t="n">
         <v>1.592691457440099</v>
       </c>
@@ -32081,9 +31883,6 @@
       <c r="O169" t="n">
         <v>64</v>
       </c>
-      <c r="Q169" t="n">
-        <v>0</v>
-      </c>
       <c r="R169" t="n">
         <v>1.210124964310768</v>
       </c>
@@ -32477,9 +32276,6 @@
       <c r="O171" t="n">
         <v>69</v>
       </c>
-      <c r="Q171" t="n">
-        <v>0</v>
-      </c>
       <c r="R171" t="n">
         <v>1.465276140844891</v>
       </c>
@@ -33169,9 +32965,6 @@
       <c r="O175" t="n">
         <v>47</v>
       </c>
-      <c r="Q175" t="n">
-        <v>0</v>
-      </c>
       <c r="R175" t="n">
         <v>0.8886855206657199</v>
       </c>
@@ -33565,9 +33358,6 @@
       <c r="O177" t="n">
         <v>71</v>
       </c>
-      <c r="Q177" t="n">
-        <v>0</v>
-      </c>
       <c r="R177" t="n">
         <v>1.507747913043294</v>
       </c>
@@ -34257,9 +34047,6 @@
       <c r="O181" t="n">
         <v>71</v>
       </c>
-      <c r="Q181" t="n">
-        <v>0</v>
-      </c>
       <c r="R181" t="n">
         <v>1.342482382282258</v>
       </c>
@@ -34653,9 +34440,6 @@
       <c r="O183" t="n">
         <v>108</v>
       </c>
-      <c r="Q183" t="n">
-        <v>0</v>
-      </c>
       <c r="R183" t="n">
         <v>2.293475698713742</v>
       </c>
@@ -35345,9 +35129,6 @@
       <c r="O187" t="n">
         <v>82</v>
       </c>
-      <c r="Q187" t="n">
-        <v>0</v>
-      </c>
       <c r="R187" t="n">
         <v>1.543274644355181</v>
       </c>
@@ -35741,9 +35522,6 @@
       <c r="O189" t="n">
         <v>79</v>
       </c>
-      <c r="Q189" t="n">
-        <v>0</v>
-      </c>
       <c r="R189" t="n">
         <v>1.656844097891383</v>
       </c>
@@ -36433,9 +36211,6 @@
       <c r="O193" t="n">
         <v>87</v>
       </c>
-      <c r="Q193" t="n">
-        <v>0</v>
-      </c>
       <c r="R193" t="n">
         <v>1.637376756815863</v>
       </c>
@@ -36829,9 +36604,6 @@
       <c r="O195" t="n">
         <v>76</v>
       </c>
-      <c r="Q195" t="n">
-        <v>0</v>
-      </c>
       <c r="R195" t="n">
         <v>1.59392596759171</v>
       </c>
@@ -37521,9 +37293,6 @@
       <c r="O199" t="n">
         <v>92</v>
       </c>
-      <c r="Q199" t="n">
-        <v>0</v>
-      </c>
       <c r="R199" t="n">
         <v>1.731478869276545</v>
       </c>
@@ -37917,9 +37686,6 @@
       <c r="O201" t="n">
         <v>100</v>
       </c>
-      <c r="Q201" t="n">
-        <v>0</v>
-      </c>
       <c r="R201" t="n">
         <v>2.097271009989092</v>
       </c>
@@ -38609,9 +38375,6 @@
       <c r="O205" t="n">
         <v>78</v>
       </c>
-      <c r="Q205" t="n">
-        <v>0</v>
-      </c>
       <c r="R205" t="n">
         <v>1.467992954386636</v>
       </c>
@@ -39005,9 +38768,6 @@
       <c r="O207" t="n">
         <v>72</v>
       </c>
-      <c r="Q207" t="n">
-        <v>0</v>
-      </c>
       <c r="R207" t="n">
         <v>1.510035127192146</v>
       </c>
@@ -39697,9 +39457,6 @@
       <c r="O211" t="n">
         <v>89</v>
       </c>
-      <c r="Q211" t="n">
-        <v>0</v>
-      </c>
       <c r="R211" t="n">
         <v>1.675017601800136</v>
       </c>
@@ -40093,9 +39850,6 @@
       <c r="O213" t="n">
         <v>69</v>
       </c>
-      <c r="Q213" t="n">
-        <v>0</v>
-      </c>
       <c r="R213" t="n">
         <v>1.447116996892474</v>
       </c>
@@ -40785,9 +40539,6 @@
       <c r="O217" t="n">
         <v>74</v>
       </c>
-      <c r="Q217" t="n">
-        <v>0</v>
-      </c>
       <c r="R217" t="n">
         <v>1.392711264418091</v>
       </c>
@@ -41181,9 +40932,6 @@
       <c r="O219" t="n">
         <v>50</v>
       </c>
-      <c r="Q219" t="n">
-        <v>0</v>
-      </c>
       <c r="R219" t="n">
         <v>1.048635504994546</v>
       </c>
@@ -41873,9 +41621,6 @@
       <c r="O223" t="n">
         <v>33</v>
       </c>
-      <c r="Q223" t="n">
-        <v>0</v>
-      </c>
       <c r="R223" t="n">
         <v>0.6210739422404997</v>
       </c>
@@ -42269,9 +42014,6 @@
       <c r="O225" t="n">
         <v>55</v>
       </c>
-      <c r="Q225" t="n">
-        <v>0</v>
-      </c>
       <c r="R225" t="n">
         <v>1.153499055494001</v>
       </c>
@@ -42961,9 +42703,6 @@
       <c r="O229" t="n">
         <v>25</v>
       </c>
-      <c r="Q229" t="n">
-        <v>0</v>
-      </c>
       <c r="R229" t="n">
         <v>0.4705105623034089</v>
       </c>
@@ -43357,9 +43096,6 @@
       <c r="O231" t="n">
         <v>32</v>
       </c>
-      <c r="Q231" t="n">
-        <v>0</v>
-      </c>
       <c r="R231" t="n">
         <v>0.6711267231965095</v>
       </c>
@@ -44049,9 +43785,6 @@
       <c r="O235" t="n">
         <v>85</v>
       </c>
-      <c r="Q235" t="n">
-        <v>0</v>
-      </c>
       <c r="R235" t="n">
         <v>1.599735911831591</v>
       </c>
@@ -44445,9 +44178,6 @@
       <c r="O237" t="n">
         <v>68</v>
       </c>
-      <c r="Q237" t="n">
-        <v>0</v>
-      </c>
       <c r="R237" t="n">
         <v>1.426144286792583</v>
       </c>
@@ -45137,9 +44867,6 @@
       <c r="O241" t="n">
         <v>84</v>
       </c>
-      <c r="Q241" t="n">
-        <v>0</v>
-      </c>
       <c r="R241" t="n">
         <v>1.580915489339454</v>
       </c>
@@ -45533,9 +45260,6 @@
       <c r="O243" t="n">
         <v>76</v>
       </c>
-      <c r="Q243" t="n">
-        <v>0</v>
-      </c>
       <c r="R243" t="n">
         <v>1.59392596759171</v>
       </c>
@@ -46225,9 +45949,6 @@
       <c r="O247" t="n">
         <v>78</v>
       </c>
-      <c r="Q247" t="n">
-        <v>0</v>
-      </c>
       <c r="R247" t="n">
         <v>1.467992954386636</v>
       </c>
@@ -46621,9 +46342,6 @@
       <c r="O249" t="n">
         <v>73</v>
       </c>
-      <c r="Q249" t="n">
-        <v>0</v>
-      </c>
       <c r="R249" t="n">
         <v>1.531007837292037</v>
       </c>
@@ -47313,9 +47031,6 @@
       <c r="O253" t="n">
         <v>113</v>
       </c>
-      <c r="Q253" t="n">
-        <v>0</v>
-      </c>
       <c r="R253" t="n">
         <v>2.126707741611408</v>
       </c>
@@ -47709,9 +47424,6 @@
       <c r="O255" t="n">
         <v>105</v>
       </c>
-      <c r="Q255" t="n">
-        <v>0</v>
-      </c>
       <c r="R255" t="n">
         <v>2.202134560488547</v>
       </c>
@@ -48401,9 +48113,6 @@
       <c r="O259" t="n">
         <v>104</v>
       </c>
-      <c r="Q259" t="n">
-        <v>0</v>
-      </c>
       <c r="R259" t="n">
         <v>1.947982681310127</v>
       </c>
@@ -49275,9 +48984,6 @@
       <c r="O263" t="n">
         <v>92</v>
       </c>
-      <c r="Q263" t="n">
-        <v>0</v>
-      </c>
       <c r="R263" t="n">
         <v>1.905305291519476</v>
       </c>
@@ -49967,9 +49673,6 @@
       <c r="O267" t="n">
         <v>96</v>
       </c>
-      <c r="Q267" t="n">
-        <v>0</v>
-      </c>
       <c r="R267" t="n">
         <v>1.798137859670886</v>
       </c>
@@ -50602,9 +50305,6 @@
       <c r="O270" t="n">
         <v>83</v>
       </c>
-      <c r="Q270" t="n">
-        <v>0</v>
-      </c>
       <c r="R270" t="n">
         <v>1.718916730392571</v>
       </c>
@@ -51294,9 +50994,6 @@
       <c r="O274" t="n">
         <v>66</v>
       </c>
-      <c r="Q274" t="n">
-        <v>0</v>
-      </c>
       <c r="R274" t="n">
         <v>1.236219778523734</v>
       </c>
@@ -51929,9 +51626,6 @@
       <c r="O277" t="n">
         <v>92</v>
       </c>
-      <c r="Q277" t="n">
-        <v>0</v>
-      </c>
       <c r="R277" t="n">
         <v>1.905305291519476</v>
       </c>
@@ -52621,9 +52315,6 @@
       <c r="O281" t="n">
         <v>102</v>
       </c>
-      <c r="Q281" t="n">
-        <v>0</v>
-      </c>
       <c r="R281" t="n">
         <v>1.910521475900317</v>
       </c>
@@ -53256,9 +52947,6 @@
       <c r="O284" t="n">
         <v>68</v>
       </c>
-      <c r="Q284" t="n">
-        <v>0</v>
-      </c>
       <c r="R284" t="n">
         <v>1.408269128514395</v>
       </c>
@@ -53948,9 +53636,6 @@
       <c r="O288" t="n">
         <v>84</v>
       </c>
-      <c r="Q288" t="n">
-        <v>0</v>
-      </c>
       <c r="R288" t="n">
         <v>1.573370627212026</v>
       </c>
@@ -54583,9 +54268,6 @@
       <c r="O291" t="n">
         <v>69</v>
       </c>
-      <c r="Q291" t="n">
-        <v>0</v>
-      </c>
       <c r="R291" t="n">
         <v>1.428978968639607</v>
       </c>
@@ -55275,9 +54957,6 @@
       <c r="O295" t="n">
         <v>70</v>
       </c>
-      <c r="Q295" t="n">
-        <v>0</v>
-      </c>
       <c r="R295" t="n">
         <v>1.311142189343355</v>
       </c>
@@ -55910,9 +55589,6 @@
       <c r="O298" t="n">
         <v>55</v>
       </c>
-      <c r="Q298" t="n">
-        <v>0</v>
-      </c>
       <c r="R298" t="n">
         <v>1.139041206886643</v>
       </c>
@@ -56602,9 +56278,6 @@
       <c r="O302" t="n">
         <v>35</v>
       </c>
-      <c r="Q302" t="n">
-        <v>0</v>
-      </c>
       <c r="R302" t="n">
         <v>0.6555710946716773</v>
       </c>
@@ -57237,9 +56910,6 @@
       <c r="O305" t="n">
         <v>30</v>
       </c>
-      <c r="Q305" t="n">
-        <v>0</v>
-      </c>
       <c r="R305" t="n">
         <v>0.6212952037563508</v>
       </c>
@@ -57929,9 +57599,6 @@
       <c r="O309" t="n">
         <v>27</v>
       </c>
-      <c r="Q309" t="n">
-        <v>0</v>
-      </c>
       <c r="R309" t="n">
         <v>0.5057262730324368</v>
       </c>
@@ -58564,9 +58231,6 @@
       <c r="O312" t="n">
         <v>27</v>
       </c>
-      <c r="Q312" t="n">
-        <v>0</v>
-      </c>
       <c r="R312" t="n">
         <v>0.5591656833807157</v>
       </c>
@@ -59256,9 +58920,6 @@
       <c r="O316" t="n">
         <v>55</v>
       </c>
-      <c r="Q316" t="n">
-        <v>0</v>
-      </c>
       <c r="R316" t="n">
         <v>1.030183148769779</v>
       </c>
@@ -59891,9 +59552,6 @@
       <c r="O319" t="n">
         <v>56</v>
       </c>
-      <c r="Q319" t="n">
-        <v>0</v>
-      </c>
       <c r="R319" t="n">
         <v>1.159751047011855</v>
       </c>
@@ -60583,9 +60241,6 @@
       <c r="O323" t="n">
         <v>78</v>
       </c>
-      <c r="Q323" t="n">
-        <v>0</v>
-      </c>
       <c r="R323" t="n">
         <v>1.460987010982595</v>
       </c>
@@ -61218,9 +60873,6 @@
       <c r="O326" t="n">
         <v>74</v>
       </c>
-      <c r="Q326" t="n">
-        <v>0</v>
-      </c>
       <c r="R326" t="n">
         <v>1.532528169265665</v>
       </c>
@@ -61910,9 +61562,6 @@
       <c r="O330" t="n">
         <v>71</v>
       </c>
-      <c r="Q330" t="n">
-        <v>0</v>
-      </c>
       <c r="R330" t="n">
         <v>1.32987279204826</v>
       </c>
@@ -62545,9 +62194,6 @@
       <c r="O333" t="n">
         <v>71</v>
       </c>
-      <c r="Q333" t="n">
-        <v>0</v>
-      </c>
       <c r="R333" t="n">
         <v>1.47039864889003</v>
       </c>
@@ -63237,9 +62883,6 @@
       <c r="O337" t="n">
         <v>64</v>
       </c>
-      <c r="Q337" t="n">
-        <v>0</v>
-      </c>
       <c r="R337" t="n">
         <v>1.198758573113924</v>
       </c>
@@ -63871,9 +63514,6 @@
       </c>
       <c r="O340" t="n">
         <v>80</v>
-      </c>
-      <c r="Q340" t="n">
-        <v>0</v>
       </c>
       <c r="R340" t="n">
         <v>1.656787210016935</v>
